--- a/practicavial-questions.xlsx
+++ b/practicavial-questions.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,17 +425,17 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">17
-En vías fuera de poblado que no dispongan de espacio especialmente reservado para ellos, ¿qué peatones deben circular por su derecha y obedecer las señales dirigidas a los conductores?</v>
+        <v xml:space="preserve">1
+Un ciclomotor ocupado por dos personas, ¿puede utilizar normalmente un carril VAO?</v>
       </c>
       <c r="E2" t="str">
-        <v>https://teorica.practicavial.com/question/794431be-294b-4cdf-8734-d46deb3f4536-1653064173-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/27734849-a0ff-4a39-92a5-8cf35beb673b-1652276778-i.jpg</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -446,20 +446,20 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-En un tramo de vía de doble sentido, si no va a adelantar, ¿en qué caso deberá guardar una distancia mínima de 50 metros con el vehículo de delante?</v>
+        <v xml:space="preserve">1
+En esta calle no hay señal de limitación de velocidad. ¿A qué velocidad máxima se puede circular?</v>
       </c>
       <c r="E3" t="str">
-        <v>https://teorica.practicavial.com/question/28a7c2b4-c748-4ade-9a1d-d839c9d8d798-1652208114-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/f0655c82-801a-499e-87fc-d3046ef3a4e2-1653072039-i.jpg</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -467,17 +467,17 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">17
-Como norma general, ¿Qué vehículos tienen permitida la circulación por las aceras?</v>
+        <v xml:space="preserve">1
+Los vehículos de tracción animal, ¿pueden circular por autopistas y autovías?</v>
       </c>
       <c r="E4" t="str">
-        <v>https://teorica.practicavial.com/question/f869f160-a1da-4046-9d25-4beb09832758-1649181098-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/c91f4674-1a2e-4008-828e-c63d051c2c2f-1656523656-i.jpg</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -488,17 +488,17 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="str" xml:space="preserve">
-        <v xml:space="preserve">17
-En las calzadas con dos sentidos y tres carriles, cuando quiera girar a la izquierda, ¿dónde debe colocarse?</v>
+        <v xml:space="preserve">2
+El vehículo de bomberos circula en servicio urgente, ¿deberá obedecer las indicaciones de los agentes?</v>
       </c>
       <c r="E5" t="str">
-        <v>https://teorica.practicavial.com/question/6ad0eb57-34fc-4a0e-a728-5b73767c1c93-1653064259-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/1346a072-bc8c-4c2f-87c3-9e2fef3aa7cb-1657205059-i.jpg</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -509,17 +509,17 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-En esta vía urbana que dispone de plataforma única de calzada y acera, en la que no existe señalización específica de velocidad, ¿a qué velocidad máxima se puede circular?</v>
+        <v xml:space="preserve">3
+En una autopista de tres carriles, el carril derecho está libre, ¿por que carril debe circular?</v>
       </c>
       <c r="E6" t="str">
-        <v>https://teorica.practicavial.com/question/2958a5de-c918-4372-96e2-840cb3f50ccb-1653070975-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/6f831673-bdfc-427a-b268-aafb02e27abf-1652278051-i.jpg</v>
       </c>
       <c r="F6">
         <v>3</v>
@@ -530,17 +530,17 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-Cuando se aproxima a un puente móvil, ¿qué debe hacer?</v>
+        <v xml:space="preserve">4
+Para evitar colisionar con el vehículo que circula delante, ¿qué es lo más importante?</v>
       </c>
       <c r="E7" t="str">
-        <v>https://teorica.practicavial.com/question/771a85d4-c3d0-4d8f-b39e-f6efefb31159-1658137427-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/5e634509-d2e1-41b1-8f77-83e6de5f22a1-1652207605-i.jpg</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -554,14 +554,14 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-Por un carril para vehículos de alta ocupación (VAO), ¿le está permitido circular a un vehículo mixto adaptable?</v>
+        <v xml:space="preserve">5
+En autopistas y autovías, ¿qué vehículos pueden superar la velocidad máxima permitida para adelantar?</v>
       </c>
       <c r="E8" t="str">
-        <v>https://teorica.practicavial.com/question/cefc9db7-9349-428d-bdb5-246d0679f5e5-1652198520-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/6dae8ad0-997f-499f-adb9-a17353aa2275-1653064267-i.jpg</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -572,17 +572,17 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="str" xml:space="preserve">
-        <v xml:space="preserve">21
-En esta vía de doble sentido, ¿qué vehículos deben dejar una separación mínima de 50 metros con el vehículo de delante cuando no pretendan adelantar?</v>
+        <v xml:space="preserve">1
+Por obras en la calzada se ha abierto un carril en sentido contrario al normal. ¿Puede circular por él un turismo con remolque?</v>
       </c>
       <c r="E9" t="str">
-        <v>https://teorica.practicavial.com/question/e0ad6122-3444-4aab-9cdc-2a104cd9731f-1652207527-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/4dfa3bbc-5987-48ab-862c-d03cdc3cf9bc-1652204191-i.jpg</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -599,11 +599,11 @@
         <v>1</v>
       </c>
       <c r="D10" t="str" xml:space="preserve">
-        <v xml:space="preserve">17
-En este tramo de autovía, ¿se puede circular a más de 100 km/h para adelantar?</v>
+        <v xml:space="preserve">1
+Los vehículos prioritarios, ¿tienen prioridad de paso sobre el resto de los usuarios de la vía?</v>
       </c>
       <c r="E10" t="str">
-        <v>https://teorica.practicavial.com/question/62aeca71-ea67-4625-8eb4-7652eba47a51-1649351736-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/d3660d71-8367-4748-bf55-e7e1d1b83c2a-1657732162-i.jpg</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -614,17 +614,17 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="str" xml:space="preserve">
-        <v xml:space="preserve">17
-Al aproximarse a ciclos circulando, ¿qué precauciones se deben tomar?</v>
+        <v xml:space="preserve">2
+Cuando un carril está delimitado a ambos lados por doble línea discontinua, ¿qué deben hacer los conductores?</v>
       </c>
       <c r="E11" t="str">
-        <v>https://teorica.practicavial.com/question/25e624bf-6119-4c25-8c78-3c9d5b7aab40-1657730355-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/1fc5a1ac-6224-4950-94f8-0c169be76437-1652199875-i.jpg</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -635,17 +635,17 @@
         <v>1</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-En un estrechamiento sin señalizar donde no es posible el cruce simultáneo, coinciden dos vehículos, ¿quién pasará primero como norma general, si el tramo es llano?</v>
+        <v xml:space="preserve">1
+Los vehículos de movilidad personal (VMP), ¿pueden tener sillín?</v>
       </c>
       <c r="E12" t="str">
-        <v>https://teorica.practicavial.com/question/3b9791b4-8a96-490c-abae-9199967c2cf5-1657732412-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/a8ece283-95e6-432a-a8ee-b0933bdfe88f-1734362196-i.jpg</v>
       </c>
       <c r="F12">
         <v>3</v>
@@ -659,14 +659,14 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-Este conjunto de vehículos con remolque de 750 kg de MMA, ¿a qué velocidad puede circular como máximo en una autovía?</v>
+        <v xml:space="preserve">2
+Se acerca a una glorieta, no hay señales de preferencia. ¿A qué vehículos debe ceder el paso?</v>
       </c>
       <c r="E13" t="str">
-        <v>https://teorica.practicavial.com/question/0be5272d-9628-4c60-9916-5fb8aea45436-1653063914-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/ac59b189-de33-4a12-a187-aa6cee6b5a0c-1657730178-i.jpg</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -677,17 +677,17 @@
         <v>1</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="str" xml:space="preserve">
-        <v xml:space="preserve">17
-Los conductores de bicicletas mayores de 14 años, ¿pueden circular por los arcenes de las autovías?</v>
+        <v xml:space="preserve">3
+El vehículo de la fotografía tiene encendida únicamente la señalización luminosa, ¿tiene prioridad de paso?</v>
       </c>
       <c r="E14" t="str">
-        <v>https://teorica.practicavial.com/question/5649301c-7b7e-493d-a62a-79b0c1ee1375-1653064129-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/2802cedc-c424-45e7-b81b-7228850d391c-1657732067-i.jpg</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -698,17 +698,17 @@
         <v>1</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-Con una motocicleta de hasta 125 centímetros cúbicos, ¿a qué velocidad máxima puede circular por una autovía?</v>
+        <v xml:space="preserve">1
+En esta vía se ha habilitado un carril adicional; ¿a qué velocidad como máximo circulará el vehículo naranja?</v>
       </c>
       <c r="E15" t="str">
-        <v>https://teorica.practicavial.com/question/c13d0716-209e-4fd0-b919-5d9fcce25b97-1653063931-i.jpg</v>
+        <v>https://teorica.practicavial.com/question/6d098241-d6c3-4447-834e-c7468ef53b51-1652200397-i.jpg</v>
       </c>
       <c r="F15">
         <v>3</v>
@@ -719,32 +719,158 @@
         <v>1</v>
       </c>
       <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" t="str" xml:space="preserve">
+        <v xml:space="preserve">2
+Circula por un carril delimitado por marcas longitudinales dobles discontinuas en vía urbana, ¿qué precauciones debe adoptar?</v>
+      </c>
+      <c r="E16" t="str">
+        <v>https://teorica.practicavial.com/question/8623a278-3eb4-4f75-b6fc-67bf482ba04a-1652199968-i.jpg</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="str" xml:space="preserve">
+        <v xml:space="preserve">3
+En el túnel de la imagen, si no pretende adelantar, ¿qué distancia de seguridad debe mantener con el vehículo de delante?</v>
+      </c>
+      <c r="E17" t="str">
+        <v>https://teorica.practicavial.com/question/495b3242-0f14-433e-836d-1db9601a074b-1652271674-i.jpg</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" t="str" xml:space="preserve">
+        <v xml:space="preserve">4
+En un vehículo de movilidad personal, ¿puede sustituirse alguna luz por un catadióptrico?</v>
+      </c>
+      <c r="E18" t="str">
+        <v>https://teorica.practicavial.com/question/94e6ca16-d671-4242-b2fe-6505984cb304-1734361265-i.jpg</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" t="str" xml:space="preserve">
+        <v xml:space="preserve">5
+Al adelantar. ¿Cuándo debe volver al carril derecho?</v>
+      </c>
+      <c r="E19" t="str">
+        <v>https://teorica.practicavial.com/question/240c66b0-e723-4b70-ae07-e9533a2edbb8-1657810047-i.jpg</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="str" xml:space="preserve">
+        <v xml:space="preserve">1
+En un tramo de vía muy estrecho en el que no esta señalizada la prioridad de paso, se encuentran un camión y un turismo. ¿Qué vehículo pasara primero?</v>
+      </c>
+      <c r="E20" t="str">
+        <v>https://teorica.practicavial.com/question/dbbceacd-35ae-4d72-8bbd-d5531f67f23e-1657732471-i.jpg</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="str" xml:space="preserve">
+        <v xml:space="preserve">2
+En esta situación, ¿tienen prioridad de paso los animales sobre el vehículo?</v>
+      </c>
+      <c r="E21" t="str">
+        <v>https://teorica.practicavial.com/question/c2744604-9eb1-4bbc-a816-fce3876cac13-1657731927-i.jpg</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22">
         <v>16</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="str" xml:space="preserve">
-        <v xml:space="preserve">16
-Para mejorar la fluidez, en una autovía se ha abierto un carril para circular en sentido contrario al habitual, ¿a qué velocidad máxima se puede circular por dicho carril?</v>
-      </c>
-      <c r="E16" t="str">
-        <v>https://teorica.practicavial.com/question/91a8f832-34c2-41dd-911c-aa41fa3f10f8-1652204251-i.jpg</v>
-      </c>
-      <c r="F16">
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="str" xml:space="preserve">
+        <v xml:space="preserve">1
+Un conductor que circula por una glorieta con tres carriles de circulación, ¿dónde debe situarse para abandonarla?</v>
+      </c>
+      <c r="E22" t="str">
+        <v>https://teorica.practicavial.com/question/3184585c-9158-4eab-8380-254e248a4db7-1650648837-i.jpg</v>
+      </c>
+      <c r="F22">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -771,7 +897,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -780,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>120 km/h.</v>
+        <v>í, porque van dos personas.</v>
       </c>
       <c r="F2" t="str">
         <v>Нет</v>
@@ -791,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -800,7 +926,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>80 km/h.</v>
+        <v>í, si circula por el arcén.</v>
       </c>
       <c r="F3" t="str">
         <v>Нет</v>
@@ -811,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -820,7 +946,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="str">
-        <v>100 km/h.</v>
+        <v>ídeo respuesta Vídeo tema Esquema Libro</v>
       </c>
       <c r="F4" t="str">
         <v>Нет</v>
@@ -831,7 +957,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -840,7 +966,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="str">
-        <v>80 km/h.</v>
+        <v>ídeo respuesta Vídeo tema Esquema Libro</v>
       </c>
       <c r="F5" t="str">
         <v>Нет</v>
@@ -851,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -860,7 +986,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="str">
-        <v>100 km/h.</v>
+        <v>eportar una mejora</v>
       </c>
       <c r="F6" t="str">
         <v>Нет</v>
@@ -871,16 +997,16 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>90 km/h.</v>
+        <v>or autopistas no, por autovías sí.</v>
       </c>
       <c r="F7" t="str">
         <v>Нет</v>
@@ -891,16 +1017,16 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="str">
-        <v>140 km/h.</v>
+        <v>ídeo respuesta Vídeo tema Esquema Libro</v>
       </c>
       <c r="F8" t="str">
         <v>Нет</v>
@@ -911,16 +1037,16 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="str">
-        <v>130 km/h.</v>
+        <v>eportar una mejora</v>
       </c>
       <c r="F9" t="str">
         <v>Нет</v>
@@ -931,16 +1057,16 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="str">
-        <v>120 km/h.</v>
+        <v>o, bajo su responsabilidad.</v>
       </c>
       <c r="F10" t="str">
         <v>Нет</v>
@@ -951,16 +1077,16 @@
         <v>1</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="str">
-        <v>60 km/h.</v>
+        <v>o, si no pone en peligro a ningún usuario de la vía.</v>
       </c>
       <c r="F11" t="str">
         <v>Нет</v>
@@ -971,16 +1097,16 @@
         <v>1</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="str">
-        <v>una velocidad inferior a un tercio con respecto de la genérica de la vía.</v>
+        <v>í, siempre.</v>
       </c>
       <c r="F12" t="str">
         <v>Нет</v>
@@ -991,16 +1117,16 @@
         <v>1</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="str">
-        <v>80 km/h.</v>
+        <v>or el derecho como norma general.</v>
       </c>
       <c r="F13" t="str">
         <v>Нет</v>
@@ -1011,16 +1137,16 @@
         <v>1</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="str">
-        <v>20 km/h.</v>
+        <v>or el central siempre si la autopista está dentro de poblado</v>
       </c>
       <c r="F14" t="str">
         <v>Нет</v>
@@ -1031,16 +1157,16 @@
         <v>1</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="str">
-        <v>30 km/h.</v>
+        <v>or el izquierdo .</v>
       </c>
       <c r="F15" t="str">
         <v>Нет</v>
@@ -1051,16 +1177,16 @@
         <v>1</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="str">
-        <v>50 km/h.</v>
+        <v>ue el vehículo disponga de ABS.</v>
       </c>
       <c r="F16" t="str">
         <v>Нет</v>
@@ -1071,16 +1197,16 @@
         <v>1</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="str">
-        <v>140 km/h.</v>
+        <v>ircular a una velocidad constante.</v>
       </c>
       <c r="F17" t="str">
         <v>Нет</v>
@@ -1091,16 +1217,16 @@
         <v>1</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" t="str">
-        <v>120 km/h.</v>
+        <v>antener una distancia frontal de seguridad suficiente.</v>
       </c>
       <c r="F18" t="str">
         <v>Нет</v>
@@ -1111,16 +1237,16 @@
         <v>1</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="str">
-        <v>100 km/h.</v>
+        <v>os turismos y las motocicletas únicamente.</v>
       </c>
       <c r="F19" t="str">
         <v>Нет</v>
@@ -1134,13 +1260,13 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="str">
-        <v>100 kilómetros por hora.</v>
+        <v>o puede superarla ningún vehículo.</v>
       </c>
       <c r="F20" t="str">
         <v>Нет</v>
@@ -1154,13 +1280,13 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="str">
-        <v>90 kilómetros por hora.</v>
+        <v>olamente las motocicletas.</v>
       </c>
       <c r="F21" t="str">
         <v>Нет</v>
@@ -1171,16 +1297,16 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="str">
-        <v>80 kilómetros por hora.</v>
+        <v>í, pero solo si el remolque es ligero.</v>
       </c>
       <c r="F22" t="str">
         <v>Нет</v>
@@ -1191,16 +1317,16 @@
         <v>1</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="str">
-        <v>la mitad de la genérica señalada para cada categoría de vehículos.</v>
+        <v>o, sólo pueden hacerlo turismos y motocicletas.</v>
       </c>
       <c r="F23" t="str">
         <v>Нет</v>
@@ -1211,16 +1337,16 @@
         <v>1</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="str">
-        <v>140 km/h.</v>
+        <v>í, cuando no lo prohíban otras señales.</v>
       </c>
       <c r="F24" t="str">
         <v>Нет</v>
@@ -1231,16 +1357,16 @@
         <v>1</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="str">
-        <v>110 km/h.</v>
+        <v>í, siempre.</v>
       </c>
       <c r="F25" t="str">
         <v>Нет</v>
@@ -1257,10 +1383,10 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="str">
-        <v>los peatones que utilicen monopatines o patines en ningún caso les está permitido...</v>
+        <v>o, nunca.</v>
       </c>
       <c r="F26" t="str">
         <v>Нет</v>
@@ -1277,10 +1403,10 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="str">
-        <v>la mitad de la mínima permitida en la vía por la que transiten.</v>
+        <v>ólo cuando circulen en servicio de urgencia.</v>
       </c>
       <c r="F27" t="str">
         <v>Нет</v>
@@ -1294,13 +1420,13 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="str">
-        <v>un vehículo prioritario que circula en servicio de urgencia se le facilitará el paso...</v>
+        <v>tilizarlo sólo para adelantar a una velocidad máxima de 80 kilómetros por hora.</v>
       </c>
       <c r="F28" t="str">
         <v>Нет</v>
@@ -1311,16 +1437,16 @@
         <v>1</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="str">
-        <v>110 km/h.</v>
+        <v>o circular por él porque la circulación está prohibida.</v>
       </c>
       <c r="F29" t="str">
         <v>Нет</v>
@@ -1331,16 +1457,16 @@
         <v>1</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="str">
-        <v>90 km/h.</v>
+        <v>ntre otras normas, si la circulación está regulada por semáforos de carril, obedecer sus indicaciones.</v>
       </c>
       <c r="F30" t="str">
         <v>Нет</v>
@@ -1351,16 +1477,16 @@
         <v>1</v>
       </c>
       <c r="B31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="str">
-        <v>100 km/h.</v>
+        <v>í, sí tiene un sistema de autoequilibrado.</v>
       </c>
       <c r="F31" t="str">
         <v>Нет</v>
@@ -1371,16 +1497,16 @@
         <v>1</v>
       </c>
       <c r="B32">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="str">
-        <v>la mínima y máxima genérica establecida para el tipo de vía por la que circula.</v>
+        <v>í, sí tiene tres ruedas.</v>
       </c>
       <c r="F32" t="str">
         <v>Нет</v>
@@ -1391,16 +1517,16 @@
         <v>1</v>
       </c>
       <c r="B33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="str">
-        <v>los que entren por la izquierda.</v>
+        <v>ídeo respuesta Vídeo tema Esquema 1 Esquema 2 Libro</v>
       </c>
       <c r="F33" t="str">
         <v>Нет</v>
@@ -1411,16 +1537,16 @@
         <v>1</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="str">
-        <v>los que entren por la derecha.</v>
+        <v>ninguno, porque yo circulo por la vía principal.</v>
       </c>
       <c r="F34" t="str">
         <v>Нет</v>
@@ -1434,13 +1560,13 @@
         <v>13</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="str">
-        <v>100 km/h.</v>
+        <v>los que circulan dentro de la glorieta.</v>
       </c>
       <c r="F35" t="str">
         <v>Нет</v>
@@ -1454,13 +1580,13 @@
         <v>13</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="str">
-        <v>120 km/h.</v>
+        <v>los que quieran acceder a la glorieta por la vía de la derecha.</v>
       </c>
       <c r="F36" t="str">
         <v>Нет</v>
@@ -1474,13 +1600,13 @@
         <v>13</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="str">
-        <v>90 km/h.</v>
+        <v>í, porque está en una vía urbana.</v>
       </c>
       <c r="F37" t="str">
         <v>Нет</v>
@@ -1491,16 +1617,16 @@
         <v>1</v>
       </c>
       <c r="B38">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="str">
-        <v>80 kilómetros por hora.</v>
+        <v>o, porque no lleva la señalización óptica y acústica simultáneamente.</v>
       </c>
       <c r="F38" t="str">
         <v>Нет</v>
@@ -1511,16 +1637,16 @@
         <v>1</v>
       </c>
       <c r="B39">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="str">
-        <v>60 kilómetros por hora.</v>
+        <v>í, siempre que la omisión de la señal acústica no entrañe peligro alguno para los demás usuarios.</v>
       </c>
       <c r="F39" t="str">
         <v>Нет</v>
@@ -1537,10 +1663,10 @@
         <v>1</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" t="str">
-        <v>la genérica de la vía.</v>
+        <v>80 kilómetros por hora.</v>
       </c>
       <c r="F40" t="str">
         <v>Нет</v>
@@ -1551,16 +1677,16 @@
         <v>1</v>
       </c>
       <c r="B41">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="str">
-        <v>90 kilómetros por hora.</v>
+        <v>60 kilómetros por hora.</v>
       </c>
       <c r="F41" t="str">
         <v>Нет</v>
@@ -1571,16 +1697,16 @@
         <v>1</v>
       </c>
       <c r="B42">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="str">
-        <v>80 kilómetros por hora.</v>
+        <v>la genérica de la vía.</v>
       </c>
       <c r="F42" t="str">
         <v>Нет</v>
@@ -1591,16 +1717,16 @@
         <v>1</v>
       </c>
       <c r="B43">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="str">
-        <v>120 kilómetros por hora.</v>
+        <v>ncender la luz de cruce o corto alcance, tanto de día como de noche, y no invadir el carril situado más a la izquierda.</v>
       </c>
       <c r="F43" t="str">
         <v>Нет</v>
@@ -1611,16 +1737,16 @@
         <v>1</v>
       </c>
       <c r="B44">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="str">
-        <v>100 Kilómetros por hora.</v>
+        <v>ncender la señal de emergencia, además de la luz de cruce, tanto de día como de noche.</v>
       </c>
       <c r="F44" t="str">
         <v>Нет</v>
@@ -1631,16 +1757,16 @@
         <v>1</v>
       </c>
       <c r="B45">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="str">
-        <v>90 Kilómetros por hora.</v>
+        <v>ircular como mínimo a 60 km/h y como máximo a 80 km/h.</v>
       </c>
       <c r="F45" t="str">
         <v>Нет</v>
@@ -1651,24 +1777,364 @@
         <v>1</v>
       </c>
       <c r="B46">
+        <v>14</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" t="str">
+        <v>a que permita una visibilidad suficiente.</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47">
+        <v>14</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47" t="str">
+        <v>ídeo respuesta Vídeo tema Esquema Libro</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48">
+        <v>14</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" t="str">
+        <v>eportar una mejora</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49">
+        <v>14</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49" t="str">
+        <v>í, la delantera.</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>1</v>
+      </c>
+      <c r="B50">
+        <v>14</v>
+      </c>
+      <c r="C50">
+        <v>4</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50" t="str">
+        <v>í, la trasera.</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51" t="str">
+        <v>o, ninguna.</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52">
+        <v>14</v>
+      </c>
+      <c r="C52">
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="str">
+        <v>uando el vehículo adelantado se encuentre al menos a 100 metros.</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>1</v>
+      </c>
+      <c r="B53">
+        <v>14</v>
+      </c>
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="E53" t="str">
+        <v>usto al rebasar al vehículo adelantado, aunque tenga que a reducir su velocidad.</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54">
+        <v>14</v>
+      </c>
+      <c r="C54">
+        <v>5</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54" t="str">
+        <v>an pronto como sea posible y sin molestar al vehículo adelantado.</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>1</v>
+      </c>
+      <c r="B55">
+        <v>15</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55" t="str">
+        <v>l turismo, porque tiene menor dificultad de maniobra.</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56">
+        <v>15</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56" t="str">
+        <v>l que tenga que dar marcha atrás menor distancia.</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>1</v>
+      </c>
+      <c r="B57">
+        <v>15</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57" t="str">
+        <v>l camión, si no se sabe qué vehículo entró primero.</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>1</v>
+      </c>
+      <c r="B58">
+        <v>15</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58" t="str">
+        <v>í, porque la señalización les da prioridad.</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59" t="str">
+        <v>í, porque el vehículo está cambiando de dirección.</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>1</v>
+      </c>
+      <c r="B60">
+        <v>15</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" t="str">
+        <v>o, los animales en la calzada nunca tienen prioridad de paso.</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>1</v>
+      </c>
+      <c r="B61">
         <v>16</v>
       </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46" t="str">
-        <v>80 Kilómetros por hora.</v>
-      </c>
-      <c r="F46" t="str">
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="str">
+        <v>n el carril derecho.</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>1</v>
+      </c>
+      <c r="B62">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62" t="str">
+        <v>n cualquier carril, aunque corte la trayectoria a otros usuarios.</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Нет</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>1</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>3</v>
+      </c>
+      <c r="E63" t="str">
+        <v>n el carril central.</v>
+      </c>
+      <c r="F63" t="str">
         <v>Нет</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F46"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F63"/>
   </ignoredErrors>
 </worksheet>
 </file>